--- a/events/Prague_2023_WC/Prague_2023_WC_start.xlsx
+++ b/events/Prague_2023_WC/Prague_2023_WC_start.xlsx
@@ -37517,6 +37517,11 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
+      <c r="X631" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -41456,6 +41461,11 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
+      <c r="X689" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -43287,6 +43297,11 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
+      <c r="X716" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -44048,6 +44063,11 @@
       <c r="R727" t="inlineStr">
         <is>
           <t>FISEROVA Tereza</t>
+        </is>
+      </c>
+      <c r="X727" t="inlineStr">
+        <is>
+          <t>42016</t>
         </is>
       </c>
     </row>
